--- a/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_ContestStartListDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eb85b1299b9076c2/ドキュメント/Unity/Okashi_Atlier2/Assets/Resources/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC52975D-EC6A-4E84-BC3F-EA25A9DDD27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FC52975D-EC6A-4E84-BC3F-EA25A9DDD27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{120FB917-76AD-4A95-902F-B704C0522CEF}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="1350" windowWidth="21915" windowHeight="13455" activeTab="2" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
+    <workbookView xWindow="3270" yWindow="1650" windowWidth="23295" windowHeight="13305" activeTab="1" xr2:uid="{1DCE2773-8A3B-4011-B3F4-E2EABC03DB8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Or_Contest_001" sheetId="1" r:id="rId1"/>
@@ -1990,48 +1990,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>◆魔法のお菓子限定◆
-魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
-フシギで芸術的な魔法のおかしを見せてください！</t>
-    <rPh sb="1" eb="3">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>シア</t>
-    </rPh>
-    <rPh sb="19" eb="22">
-      <t>イップウカ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>ボシュウ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>ゲイジュツ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>マホウ</t>
-    </rPh>
-    <rPh sb="53" eb="54">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>◆自由課題◆
 春エリアで行われるパティシエ中～上級向けのコンテスト。難易度高め。
 春の大妖精様を讃えるお菓子を希望します。</t>
@@ -2350,6 +2308,45 @@
   </si>
   <si>
     <t>t204</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>◆魔法のお菓子限定◆
+魔法で仕上げた、一風変わったオシャレなお菓子を募集♪
+フシギで芸術的なおかしを見せてください！</t>
+    <rPh sb="1" eb="3">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>シア</t>
+    </rPh>
+    <rPh sb="19" eb="22">
+      <t>イップウカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ボシュウ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>ゲイジュツ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ミ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3278,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X6" t="s">
         <v>99</v>
@@ -3491,7 +3488,7 @@
         <v>138</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -3665,7 +3662,7 @@
         <v>120</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -3752,7 +3749,7 @@
         <v>139</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -4732,7 +4729,7 @@
         <v>148</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -4867,13 +4864,13 @@
         <v>0</v>
       </c>
       <c r="W11" t="s">
+        <v>216</v>
+      </c>
+      <c r="X11" t="s">
         <v>217</v>
       </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
         <v>218</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>219</v>
       </c>
       <c r="Z11">
         <v>6</v>
@@ -4906,7 +4903,7 @@
         <v>149</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5151,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X2" t="s">
         <v>127</v>
@@ -5238,10 +5235,10 @@
         <v>0</v>
       </c>
       <c r="W3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y3" t="s">
         <v>101</v>
@@ -5499,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="W6" t="s">
+        <v>214</v>
+      </c>
+      <c r="X6" t="s">
         <v>215</v>
-      </c>
-      <c r="X6" t="s">
-        <v>216</v>
       </c>
       <c r="Y6" t="s">
         <v>101</v>
@@ -5673,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="s">
+        <v>225</v>
+      </c>
+      <c r="X8" t="s">
         <v>226</v>
-      </c>
-      <c r="X8" t="s">
-        <v>227</v>
       </c>
       <c r="Y8" t="s">
         <v>101</v>
@@ -5712,7 +5709,7 @@
         <v>153</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -5886,7 +5883,7 @@
         <v>154</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -6060,7 +6057,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H13">
         <v>0</v>
